--- a/pigment.xlsx
+++ b/pigment.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6001c253a683c1d7/桌面/Sales Report/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="232" documentId="8_{F6E71FFD-FC9E-467B-B15C-9E6880C3800B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6645AF43-F4EF-4337-B4F3-4413E5D31826}"/>
+  <xr:revisionPtr revIDLastSave="241" documentId="8_{F6E71FFD-FC9E-467B-B15C-9E6880C3800B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B41A75AB-747F-4577-8B8A-44225DB1C49B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="79">
   <si>
     <t>色號</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -355,6 +355,10 @@
   </si>
   <si>
     <t>PO64</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>~</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1224,7 +1228,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -1256,7 +1260,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -1288,7 +1292,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>22</v>
       </c>
@@ -1320,7 +1324,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -1352,7 +1356,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -1384,7 +1388,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -1416,7 +1420,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>72</v>
       </c>
@@ -1448,7 +1452,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>19</v>
       </c>
@@ -1480,7 +1484,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>18</v>
       </c>
@@ -1512,7 +1516,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>59</v>
       </c>
@@ -1544,7 +1548,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>29</v>
       </c>
@@ -1576,7 +1580,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>28</v>
       </c>
@@ -1640,7 +1644,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>26</v>
       </c>
@@ -2120,7 +2124,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>52</v>
       </c>
@@ -2131,25 +2135,25 @@
         <v>39</v>
       </c>
       <c r="D45" s="1">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="E45" s="1">
-        <v>78.099999999999994</v>
+        <v>79.2</v>
       </c>
       <c r="F45" s="1">
+        <v>6</v>
+      </c>
+      <c r="G45" s="1">
         <v>7</v>
       </c>
-      <c r="G45" s="1">
-        <v>8</v>
-      </c>
       <c r="H45" s="1">
-        <v>290</v>
-      </c>
-      <c r="I45" s="1">
-        <v>4</v>
-      </c>
-      <c r="J45" s="1">
-        <v>5</v>
+        <v>180</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
@@ -2866,7 +2870,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>73</v>
       </c>
@@ -2898,7 +2902,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>74</v>
       </c>
@@ -2930,7 +2934,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>75</v>
       </c>
@@ -2998,23 +3002,8 @@
   <autoFilter ref="A1:J105" xr:uid="{03A264C7-87D9-410C-908A-5B6EA225BB0B}">
     <filterColumn colId="0">
       <filters>
-        <filter val="PR122"/>
-        <filter val="PR144"/>
-        <filter val="PR149"/>
-        <filter val="PR166"/>
-        <filter val="PR170(3RK"/>
-        <filter val="PR170(5RK"/>
-        <filter val="PR176"/>
-        <filter val="PR177"/>
         <filter val="PR185"/>
-        <filter val="PR208"/>
-        <filter val="PR214"/>
-        <filter val="PR242"/>
-        <filter val="PR254"/>
-        <filter val="PR48:2"/>
-        <filter val="PR48:3"/>
-        <filter val="PR53:1"/>
-        <filter val="PR57:1"/>
+        <filter val="PY185"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A17:J104">

--- a/pigment.xlsx
+++ b/pigment.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6001c253a683c1d7/桌面/Sales Report/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="241" documentId="8_{F6E71FFD-FC9E-467B-B15C-9E6880C3800B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B41A75AB-747F-4577-8B8A-44225DB1C49B}"/>
+  <xr:revisionPtr revIDLastSave="242" documentId="8_{F6E71FFD-FC9E-467B-B15C-9E6880C3800B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6FF6B4E6-8977-44A8-A8A7-211FAC0BEC14}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2135,7 +2135,7 @@
         <v>39</v>
       </c>
       <c r="D45" s="1">
-        <v>88</v>
+        <v>88.8</v>
       </c>
       <c r="E45" s="1">
         <v>79.2</v>
